--- a/data/trans_orig/IP16B10-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16B10-Estudios-trans_orig.xlsx
@@ -2713,7 +2713,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>886</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>53,58%</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>40,62%</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,3%</t>
         </is>
       </c>
     </row>
